--- a/outputs/security-lab-matrix/amr-fitness-security-vulnerability-matrix.xlsx
+++ b/outputs/security-lab-matrix/amr-fitness-security-vulnerability-matrix.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vulnerability Matrix" sheetId="1" r:id="Rac09f50ee7df433f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vulnerability Matrix" sheetId="1" r:id="Ra66fe3bd68a34a7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Test Data" sheetId="2" r:id="Rd8fc37ec3eb04983"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -46,6 +47,12 @@
       <x:i/>
       <x:sz val="11"/>
       <x:color rgb="FF334155"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -173,7 +180,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="52">
+  <x:cellXfs count="56">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -293,6 +300,16 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -579,290 +596,819 @@
         <x:v>Defensive Remediation</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="72" customHeight="1">
+    <x:row r="5" ht="76" customHeight="1">
       <x:c r="A5" s="42" t="str">
-        <x:v>Reflected XSS</x:v>
+        <x:v>Missing HTTPS</x:v>
       </x:c>
       <x:c r="B5" s="45" t="str">
         <x:v>Easy</x:v>
       </x:c>
       <x:c r="C5" s="34" t="str">
+        <x:v>A05:2021 Security Misconfiguration</x:v>
+      </x:c>
+      <x:c r="D5" s="34" t="str">
+        <x:v>1. Connect to http://localhost:3000 in browser or curl.
+2. Inspect network traffic and transport protocol.
+3. Verify HTTP plain text transmission without SSL/TLS certificates.</x:v>
+      </x:c>
+      <x:c r="E5" s="34" t="str">
+        <x:v>Cleartext credential interception on network
+Man-in-the-Middle (MitM) session hijacking
+Data tampering in transit</x:v>
+      </x:c>
+      <x:c r="F5" s="35" t="str">
+        <x:v>Enforce HTTPS/TLS encryption with SSL certificates
+Redirect HTTP traffic to HTTPS (301 Moved Permanently)
+Implement HTTP Strict Transport Security (HSTS) headers</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="76" customHeight="1">
+      <x:c r="A6" s="43" t="str">
+        <x:v>Reflected XSS</x:v>
+      </x:c>
+      <x:c r="B6" s="46" t="str">
+        <x:v>Easy</x:v>
+      </x:c>
+      <x:c r="C6" s="37" t="str">
         <x:v>A03:2021 Injection</x:v>
       </x:c>
-      <x:c r="D5" s="34" t="str">
+      <x:c r="D6" s="37" t="str">
         <x:v>1. Visit /app/classes?search=&lt;img src=x onerror=alert(1)&gt; in browser.
 2. Observe search query banner above class filter controls.
 3. Verify dangerouslySetInnerHTML renders unsanitized query and executes script.</x:v>
       </x:c>
-      <x:c r="E5" s="34" t="str">
+      <x:c r="E6" s="37" t="str">
         <x:v>Session token theft via localStorage/cookies
 DOM manipulation and phishing overlays
 Unauthorized class cancellations in victim session</x:v>
       </x:c>
-      <x:c r="F5" s="35" t="str">
+      <x:c r="F6" s="38" t="str">
         <x:v>Contextual output encoding (use React JSX {search})
 Strict Content Security Policy (CSP)
 Input sanitization via DOMPurify</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="72" customHeight="1">
-      <x:c r="A6" s="43" t="str">
-        <x:v>No rate limiting &amp; unlimited login</x:v>
-      </x:c>
-      <x:c r="B6" s="46" t="str">
+    <x:row r="7" ht="76" customHeight="1">
+      <x:c r="A7" s="43" t="str">
+        <x:v>No rate limiting</x:v>
+      </x:c>
+      <x:c r="B7" s="46" t="str">
         <x:v>Easy</x:v>
       </x:c>
-      <x:c r="C6" s="37" t="str">
-        <x:v>A07:2021 Identification &amp; Auth Failures</x:v>
-      </x:c>
-      <x:c r="D6" s="37" t="str">
-        <x:v>1. Send &gt;15 rapid POST /api/auth/login requests with invalid passwords.
-2. Inspect response status codes in Dev Tools / Postman.
-3. Verify requests return 401 without 429 throttling or lockout.</x:v>
-      </x:c>
-      <x:c r="E6" s="37" t="str">
+      <x:c r="C7" s="37" t="str">
+        <x:v>A04:2021 Insecure Design</x:v>
+      </x:c>
+      <x:c r="D7" s="37" t="str">
+        <x:v>1. Send &gt;15 rapid POST /api/auth/login or /signup requests.
+2. Inspect response HTTP status codes in Dev Tools / Postman.
+3. Verify requests process without 429 Too Many Requests status code.</x:v>
+      </x:c>
+      <x:c r="E7" s="37" t="str">
         <x:v>Automated credential stuffing &amp; password spraying
 High CPU load from bcrypt hashing
-Increased probability of account takeover</x:v>
-      </x:c>
-      <x:c r="F6" s="38" t="str">
-        <x:v>Implement express-rate-limit middleware
-Account lockout after 5 failed attempts
+Noisy monitoring and logs</x:v>
+      </x:c>
+      <x:c r="F7" s="38" t="str">
+        <x:v>Implement express-rate-limit middleware on auth routes
+Per-IP and per-account request rate caps
+Alert on anomalous request volume spikes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="76" customHeight="1">
+      <x:c r="A8" s="43" t="str">
+        <x:v>Unlimited login attempts</x:v>
+      </x:c>
+      <x:c r="B8" s="46" t="str">
+        <x:v>Easy</x:v>
+      </x:c>
+      <x:c r="C8" s="37" t="str">
+        <x:v>A07:2021 Identification &amp; Auth Failures</x:v>
+      </x:c>
+      <x:c r="D8" s="37" t="str">
+        <x:v>1. Submit 20 consecutive POST /api/auth/login requests with invalid passwords.
+2. Verify server returns 401 continuously without account lockout or progressive delay.</x:v>
+      </x:c>
+      <x:c r="E8" s="37" t="str">
+        <x:v>Increased success rate of brute-force password guessing
+Account takeover of weak passwords
+Server resource consumption</x:v>
+      </x:c>
+      <x:c r="F8" s="38" t="str">
+        <x:v>Account lockout policy after 5 consecutive failed logins
+Progressive response delay on failed attempts
 CAPTCHA verification on high frequency</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="72" customHeight="1">
-      <x:c r="A7" s="43" t="str">
-        <x:v>Open CORS &amp; exposed headers</x:v>
-      </x:c>
-      <x:c r="B7" s="46" t="str">
+    <x:row r="9" ht="76" customHeight="1">
+      <x:c r="A9" s="43" t="str">
+        <x:v>Open CORS policy &amp; exposed headers</x:v>
+      </x:c>
+      <x:c r="B9" s="46" t="str">
         <x:v>Easy</x:v>
       </x:c>
-      <x:c r="C7" s="37" t="str">
+      <x:c r="C9" s="37" t="str">
         <x:v>A05:2021 Security Misconfiguration</x:v>
       </x:c>
-      <x:c r="D7" s="37" t="str">
+      <x:c r="D9" s="37" t="str">
         <x:v>1. Send curl -I http://localhost:3000/api/system/info.
 2. Inspect response HTTP headers.
 3. Verify Access-Control-Allow-Origin: * and X-Powered-By: Express are exposed.</x:v>
       </x:c>
-      <x:c r="E7" s="37" t="str">
+      <x:c r="E9" s="37" t="str">
         <x:v>Cross-origin data leakage to arbitrary web origins
 Backend tech stack fingerprinting
 Targeted exploit selection for Express/Node</x:v>
       </x:c>
-      <x:c r="F7" s="38" t="str">
+      <x:c r="F9" s="38" t="str">
         <x:v>Restrict CORS origin strictly to trusted domains
 Disable X-Powered-By header via app.disable()
 Mount Helmet security headers middleware</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="72" customHeight="1">
-      <x:c r="A8" s="43" t="str">
+    <x:row r="10" ht="76" customHeight="1">
+      <x:c r="A10" s="43" t="str">
+        <x:v>Missing authorization checks</x:v>
+      </x:c>
+      <x:c r="B10" s="46" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="C10" s="37" t="str">
+        <x:v>A01:2021 Broken Access Control</x:v>
+      </x:c>
+      <x:c r="D10" s="37" t="str">
+        <x:v>1. Issue unauthenticated GET /api/system/export or GET /api/membership/payments/:id.
+2. Inspect API response payload.
+3. Verify raw user records, audit logs, and payments are returned without authentication.</x:v>
+      </x:c>
+      <x:c r="E10" s="37" t="str">
+        <x:v>Unauthorized administrative data export
+Privacy breaches and regulatory incidents
+Full database disclosure to unauthenticated users</x:v>
+      </x:c>
+      <x:c r="F10" s="38" t="str">
+        <x:v>Enforce requireAuth middleware across all sensitive endpoints
+Server-side authorization policies
+Deny by default endpoint permissions</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="76" customHeight="1">
+      <x:c r="A11" s="43" t="str">
         <x:v>Horizontal privilege escalation (IDOR)</x:v>
       </x:c>
-      <x:c r="B8" s="46" t="str">
+      <x:c r="B11" s="46" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="C8" s="37" t="str">
+      <x:c r="C11" s="37" t="str">
         <x:v>A01:2021 Broken Access Control</x:v>
       </x:c>
-      <x:c r="D8" s="37" t="str">
-        <x:v>1. Log in as Member 1 (member@amrfitness.local, MEM-10001).
-2. Submit GET /api/member/activity?memberId=MEM-10002 or /profile?memberId=MEM-10002.
-3. Verify API returns Member MEM-10002's private data without ownership check.</x:v>
-      </x:c>
-      <x:c r="E8" s="37" t="str">
+      <x:c r="D11" s="37" t="str">
+        <x:v>1. Log in as Member 1 (member@amrfitness.local, kmc-143).
+2. Submit GET /api/member/profile?memberId=kmc-144 or PUT /api/member/profile?memberId=kmc-144.
+3. Verify API returns Member kmc-144's private data and updates profile without ownership check.</x:v>
+      </x:c>
+      <x:c r="E11" s="37" t="str">
         <x:v>Unauthorized exposure of private workout and health data
 Potential alteration of target member profiles/bookings
 Violation of data privacy regulations</x:v>
       </x:c>
-      <x:c r="F8" s="38" t="str">
+      <x:c r="F11" s="38" t="str">
         <x:v>Strict server-side identity binding (req.user.id)
 Validate requested_member_id === session_member_id
 Deny by default authorization policies</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="72" customHeight="1">
-      <x:c r="A9" s="43" t="str">
-        <x:v>Sensitive data exposure (Password hash leak)</x:v>
-      </x:c>
-      <x:c r="B9" s="46" t="str">
+    <x:row r="12" ht="76" customHeight="1">
+      <x:c r="A12" s="43" t="str">
+        <x:v>Sensitive data exposure (Hash leak)</x:v>
+      </x:c>
+      <x:c r="B12" s="46" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="C9" s="37" t="str">
+      <x:c r="C12" s="37" t="str">
         <x:v>A02:2021 Cryptographic Failures</x:v>
       </x:c>
-      <x:c r="D9" s="37" t="str">
+      <x:c r="D12" s="37" t="str">
         <x:v>1. Issue GET /api/auth/me or GET /api/admin/members.
 2. Inspect JSON response payload under data.user.
 3. Verify passwordHash (bcrypt) and md5Hash fields are returned in plain JSON text.</x:v>
       </x:c>
-      <x:c r="E9" s="37" t="str">
+      <x:c r="E12" s="37" t="str">
         <x:v>Offline password hash cracking via dictionary attacks
 Credential reuse risk across secondary platforms
 Direct violation of credential security standards</x:v>
       </x:c>
-      <x:c r="F9" s="38" t="str">
+      <x:c r="F12" s="38" t="str">
         <x:v>DTO sanitization omitting passwordHash and md5Hash
 Apply user field masking middleware (sanitizeUser)
 Response schema validation excluding secrets</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="72" customHeight="1">
-      <x:c r="A10" s="43" t="str">
+    <x:row r="13" ht="76" customHeight="1">
+      <x:c r="A13" s="43" t="str">
         <x:v>Insecure password reset flow</x:v>
       </x:c>
-      <x:c r="B10" s="46" t="str">
+      <x:c r="B13" s="46" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="C10" s="37" t="str">
+      <x:c r="C13" s="37" t="str">
         <x:v>A07:2021 Identification &amp; Auth Failures</x:v>
       </x:c>
-      <x:c r="D10" s="37" t="str">
+      <x:c r="D13" s="37" t="str">
         <x:v>1. Submit POST /api/auth/reset-password with {"email":"admin@amrfitness.local","newPassword":"HackedAdmin@123"}.
 2. Inspect response message.
 3. Verify target account password is reset instantly without token or OTP.</x:v>
       </x:c>
-      <x:c r="E10" s="37" t="str">
+      <x:c r="E13" s="37" t="str">
         <x:v>Trivial account takeover of any user by email
 Immediate compromise of lead administrator accounts
 Unauthorized profile modifications and data loss</x:v>
       </x:c>
-      <x:c r="F10" s="38" t="str">
+      <x:c r="F13" s="38" t="str">
         <x:v>Time-limited cryptographic reset tokens via email
 Multi-factor authentication (MFA) or current password check
 Instant email alert on password reset</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="72" customHeight="1">
-      <x:c r="A11" s="43" t="str">
+    <x:row r="14" ht="76" customHeight="1">
+      <x:c r="A14" s="43" t="str">
+        <x:v>Verbose error messages &amp; stack trace leakage</x:v>
+      </x:c>
+      <x:c r="B14" s="46" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="C14" s="37" t="str">
+        <x:v>A05:2021 Security Misconfiguration</x:v>
+      </x:c>
+      <x:c r="D14" s="37" t="str">
+        <x:v>1. Send request to GET /api/system/debug/error or click System Diagnostics in footer.
+2. Inspect API response HTTP status (500 Internal Server Error) and JSON payload.
+3. Verify server leaks raw Node.js stack traces, file system paths, and internal error codes.</x:v>
+      </x:c>
+      <x:c r="E14" s="37" t="str">
+        <x:v>System internal file path and environment disclosure
+Facilitates precise targeted exploit payload creation
+Exposes internal application architecture to attackers</x:v>
+      </x:c>
+      <x:c r="F14" s="38" t="str">
+        <x:v>Generic error responses in production environments
+Log detailed stack traces to secure server-side logging systems
+Disable verbose error middleware in production builds</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="76" customHeight="1">
+      <x:c r="A15" s="43" t="str">
         <x:v>Hardcoded secret in client bundle</x:v>
       </x:c>
-      <x:c r="B11" s="46" t="str">
+      <x:c r="B15" s="46" t="str">
         <x:v>Hard</x:v>
       </x:c>
-      <x:c r="C11" s="37" t="str">
+      <x:c r="C15" s="37" t="str">
         <x:v>A05:2021 Security Misconfiguration</x:v>
       </x:c>
-      <x:c r="D11" s="37" t="str">
-        <x:v>1. Search compiled JS bundle in dist/client/assets/ for AMR_SECRET_MASTER_API_KEY.
-2. Locate AMR_SECRET_MASTER_API_KEY_2026_V1 in client bundle.
-3. Submit GET /api/admin/dashboard with header "x-admin-key: AMR_SECRET_MASTER_API_KEY_2026_V1".
-4. Verify server grants full admin access without authentication.</x:v>
-      </x:c>
-      <x:c r="E11" s="37" t="str">
-        <x:v>Complete system and administrative takeover
-Bypasses standard authentication and role checks
-Permanent compromise as long as secret is in client bundle</x:v>
-      </x:c>
-      <x:c r="F11" s="38" t="str">
-        <x:v>Zero secret client bundles (never embed master keys)
-Server-side authorization only
-Automated secret scanning (GitGuardian/TruffleHog) in CI/CD</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="72" customHeight="1">
-      <x:c r="A12" s="43" t="str">
+      <x:c r="D15" s="37" t="str">
+        <x:v>1. Open browser DevTools (F12) -&gt; Sources tab or inspect loaded JS bundle (assets/index-*.js) in Burp Suite.
+2. Search JS assets for API key references to find AMR_SECRET_MASTER_API_KEY_2026_V1.
+3. Send HTTP request to GET /api/admin/dashboard with header "x-admin-key: AMR_SECRET_MASTER_API_KEY_2026_V1".
+4. Verify backend grants full administrative privileges without authenticating.</x:v>
+      </x:c>
+      <x:c r="E15" s="37" t="str">
+        <x:v>Complete administrative takeover of the application
+Bypasses standard authentication and session controls
+Permanent backdoor exposure while secret exists in client build assets</x:v>
+      </x:c>
+      <x:c r="F15" s="38" t="str">
+        <x:v>Never embed administrative API keys or master secrets in client-side code
+Implement strict server-side authentication and session authorization
+Enforce automated secret scanning (GitGuardian/TruffleHog) in build pipelines</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="76" customHeight="1">
+      <x:c r="A16" s="43" t="str">
         <x:v>Subscription tier price bypass</x:v>
       </x:c>
-      <x:c r="B12" s="46" t="str">
+      <x:c r="B16" s="46" t="str">
         <x:v>Hard</x:v>
       </x:c>
-      <x:c r="C12" s="37" t="str">
+      <x:c r="C16" s="37" t="str">
         <x:v>A04:2021 Insecure Design</x:v>
       </x:c>
-      <x:c r="D12" s="37" t="str">
+      <x:c r="D16" s="37" t="str">
         <x:v>1. Log in as member and choose Elite tier (PLAN-10003).
 2. Intercept POST /api/membership/subscribe request payload.
 3. Inject {"planId":"PLAN-10003","pricePaise":0,"status":"active"}.
 4. Verify backend activates Elite plan for ₹0 charged.</x:v>
       </x:c>
-      <x:c r="E12" s="37" t="str">
+      <x:c r="E16" s="37" t="str">
         <x:v>Financial fraud by bypassing subscription payment gates
 Direct loss of business revenue
 Corrupted payment ledgers and accounting records</x:v>
       </x:c>
-      <x:c r="F12" s="38" t="str">
+      <x:c r="F16" s="38" t="str">
         <x:v>Server-side price lookup based on planId
 Never trust client-supplied prices or statuses
 Validate payment gateway signatures/webhooks</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="72" customHeight="1">
-      <x:c r="A13" s="43" t="str">
+    <x:row r="17" ht="76" customHeight="1">
+      <x:c r="A17" s="43" t="str">
+        <x:v>Predictable reset tokens</x:v>
+      </x:c>
+      <x:c r="B17" s="46" t="str">
+        <x:v>Hard</x:v>
+      </x:c>
+      <x:c r="C17" s="37" t="str">
+        <x:v>A07:2021 Identification &amp; Auth Failures</x:v>
+      </x:c>
+      <x:c r="D17" s="37" t="str">
+        <x:v>1. Submit POST /api/auth/forgot-password with target email.
+2. Intercept response to observe resetToken: MD5(email).
+3. Submit POST /api/auth/reset-password-with-token using token MD5(target_email).
+4. Verify target account password is reset via forged token.</x:v>
+      </x:c>
+      <x:c r="E17" s="37" t="str">
+        <x:v>Unauthorized password reset for arbitrary accounts
+Admin account takeover via forged reset tokens
+Complete auth control collapse</x:v>
+      </x:c>
+      <x:c r="F17" s="38" t="str">
+        <x:v>Cryptographically secure pseudo-random generators (CSPRNG)
+Store hashed high-entropy reset tokens server-side
+Enforce short expiration TTL (15 minutes)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="76" customHeight="1">
+      <x:c r="A18" s="43" t="str">
         <x:v>Vertical privilege escalation (Role mass assignment)</x:v>
       </x:c>
-      <x:c r="B13" s="46" t="str">
+      <x:c r="B18" s="46" t="str">
         <x:v>Hard</x:v>
       </x:c>
-      <x:c r="C13" s="37" t="str">
+      <x:c r="C18" s="37" t="str">
         <x:v>A01:2021 Broken Access Control</x:v>
       </x:c>
-      <x:c r="D13" s="37" t="str">
+      <x:c r="D18" s="37" t="str">
         <x:v>1. Log in as standard member (member@amrfitness.local).
-2. Submit PUT /api/member/profile or POST /api/auth/signup with payload {"role":"admin"}.
+2. Submit PUT /api/member/profile or POST /api/auth/signup with payload {"role":"admin"} or {"role":"trainer"}.
 3. Query GET /api/auth/me.
-4. Verify account role is upgraded to admin.</x:v>
-      </x:c>
-      <x:c r="E13" s="37" t="str">
-        <x:v>Standard member escalates privilege to full admin
+4. Verify account role is upgraded to admin or trainer.</x:v>
+      </x:c>
+      <x:c r="E18" s="37" t="str">
+        <x:v>Standard member escalates privilege to admin or trainer
 Unauthorized management of plans, trainers, and members
 Compromise of administrative audit trail</x:v>
       </x:c>
-      <x:c r="F13" s="38" t="str">
+      <x:c r="F18" s="38" t="str">
         <x:v>Strict Request DTO field allowlisting (exclude role)
 Restrict role updates to dedicated admin endpoints
 Separate internal model properties from public input</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="72" customHeight="1">
-      <x:c r="A14" s="44" t="str">
+    <x:row r="19" ht="76" customHeight="1">
+      <x:c r="A19" s="44" t="str">
         <x:v>Weak credential hashing (Legacy MD5)</x:v>
       </x:c>
-      <x:c r="B14" s="47" t="str">
+      <x:c r="B19" s="47" t="str">
         <x:v>Hard</x:v>
       </x:c>
-      <x:c r="C14" s="40" t="str">
+      <x:c r="C19" s="40" t="str">
         <x:v>A02:2021 Cryptographic Failures</x:v>
       </x:c>
-      <x:c r="D14" s="40" t="str">
+      <x:c r="D19" s="40" t="str">
         <x:v>1. Extract md5Hash field (e10adc3949ba59abbe56e057f20f883e) from API response.
 2. Supply digest to Hashcat / John / online lookup.
 3. Verify digest cracks to plain-text string "123456" in milliseconds.</x:v>
       </x:c>
-      <x:c r="E14" s="40" t="str">
+      <x:c r="E19" s="40" t="str">
         <x:v>Instant offline password cracking via dictionary attacks
 Widespread user account compromise
 Failure to comply with modern cryptographic standards</x:v>
       </x:c>
-      <x:c r="F14" s="41" t="str">
+      <x:c r="F19" s="41" t="str">
         <x:v>Use salted bcrypt (cost &gt;= 10) or Argon2id
 Deprecate legacy MD5 algorithms entirely
 Automatic re-hashing of legacy passwords on login</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="32" customHeight="1">
-      <x:c r="A16" s="51" t="str">
+    <x:row r="21" ht="32" customHeight="1">
+      <x:c r="A21" s="51" t="str">
         <x:v>Instructor reset checklist: keep the lab isolated; use only disposable data; remove /api/lab and restore security controls before reuse.</x:v>
       </x:c>
-      <x:c r="B16" s="51"/>
-      <x:c r="C16" s="51"/>
-      <x:c r="D16" s="51"/>
-      <x:c r="E16" s="51"/>
-      <x:c r="F16" s="51"/>
+      <x:c r="B21" s="51"/>
+      <x:c r="C21" s="51"/>
+      <x:c r="D21" s="51"/>
+      <x:c r="E21" s="51"/>
+      <x:c r="F21" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
-    <x:mergeCell ref="A16:F16"/>
+    <x:mergeCell ref="A21:F21"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="B5:B14">
+  <x:conditionalFormatting sqref="B5:B19">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Easy"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Medium"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Hard"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="35" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="54" t="str">
+        <x:v>AMR Fitness — Sample Working Test Data &amp; Exploit Vectors</x:v>
+      </x:c>
+      <x:c r="B1" s="54"/>
+      <x:c r="C1" s="54"/>
+      <x:c r="D1" s="54"/>
+      <x:c r="E1" s="54"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="55" t="str">
+        <x:v>Account Type</x:v>
+      </x:c>
+      <x:c r="B3" s="55" t="str">
+        <x:v>Email Address</x:v>
+      </x:c>
+      <x:c r="C3" s="55" t="str">
+        <x:v>Password</x:v>
+      </x:c>
+      <x:c r="D3" s="55" t="str">
+        <x:v>Member ID / Role</x:v>
+      </x:c>
+      <x:c r="E3" s="55" t="str">
+        <x:v>Notes / Context</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Admin Account</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>admin@amrfitness.local</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>AMR#Fitness$2026!AdminKey</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Role: admin</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>Primary lead administrator account</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Primary Member</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>member@amrfitness.local</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Member@12345</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>kmc-143 / role: member</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>Primary student member test account</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Secondary Member</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>priya.s@example.com</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Fitness@123</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>kmc-144 / role: member</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>Target member for IDOR testing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Tertiary Member</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>ananya.v@example.com</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Fitness@123</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>kmc-145 / role: member</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>Target member for IDOR testing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str"/>
+      <x:c r="B8" t="str"/>
+      <x:c r="C8" t="str"/>
+      <x:c r="D8" t="str"/>
+      <x:c r="E8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="55" t="str">
+        <x:v>Payment Category</x:v>
+      </x:c>
+      <x:c r="B9" s="55" t="str">
+        <x:v>Field Name</x:v>
+      </x:c>
+      <x:c r="C9" s="55" t="str">
+        <x:v>Sample Test Value</x:v>
+      </x:c>
+      <x:c r="D9" s="55" t="str">
+        <x:v>Format / Type</x:v>
+      </x:c>
+      <x:c r="E9" s="55" t="str">
+        <x:v>Usage Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Credit / Debit Card</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Cardholder Name</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Rahul Sharma</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>Cardholder name input</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Credit / Debit Card</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Card Number</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>4532 8912 3456 7890</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>16-digit formatted</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>Simulated Visa/Mastercard</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Credit / Debit Card</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Expiry Date</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>12/28</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>MM/YY</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>Future expiration date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Credit / Debit Card</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>CVV Code</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>3 digits</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>Security code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>UPI / Mobile</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Virtual Payment Address</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>rahul@okicici</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>VPA string</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>Sample ICICI UPI ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>UPI / Mobile</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Secondary VPA</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>member@paytm</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>VPA string</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>Sample Paytm UPI ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Net Banking</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Primary Bank Name</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>HDFC Bank NetBanking</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Select Option</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>HDFC Bank option</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Net Banking</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Customer ID</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>HDFC_USER_9941</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Text ID</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>Customer User ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="55" t="str"/>
+      <x:c r="B18" s="55" t="str"/>
+      <x:c r="C18" s="55" t="str"/>
+      <x:c r="D18" s="55" t="str"/>
+      <x:c r="E18" s="55" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Vulnerability Vectors</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Parameter / Header</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Sample Exploit Payload</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Target Endpoint</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>Expected Result</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Hardcoded Master Key</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>x-admin-key header</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>AMR_SECRET_MASTER_API_KEY_2026_V1</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>GET /api/admin/dashboard</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>Bypasses auth; grants admin session</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>IDOR Profile Access</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>memberId query param</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>kmc-144</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>GET /api/member/profile?memberId=kmc-144</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>Returns target member private profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>IDOR Profile Edit</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>memberId parameter</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>kmc-144</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>PUT /api/member/profile?memberId=kmc-144</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Updates target member profile details</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Predictable Reset Token</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>resetToken parameter</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>MD5(target_email)</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>POST /api/auth/reset-password-with-token</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>Resets target user password via forged token</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>Subscription Price Bypass</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>pricePaise body param</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>POST /api/membership/subscribe</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>Activates Elite plan for ₹0 charged</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>Mass Assignment Role</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>role body param</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>admin</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>PUT /api/member/profile</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>Escalates member role to admin</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>